--- a/backend/product_database/空調負荷基準表.xlsx
+++ b/backend/product_database/空調負荷基準表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flitt\.gemini\antigravity\scratch\ac-selection-system\backend\product_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7522A7-8E95-4C9E-A26A-9595F29ECE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D8A96D-6322-435A-860B-3E82D41F1D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{25F847D7-E8AD-4FFB-BAB5-C066C5856460}"/>
+    <workbookView xWindow="672" yWindow="0" windowWidth="17640" windowHeight="12240" activeTab="1" xr2:uid="{25F847D7-E8AD-4FFB-BAB5-C066C5856460}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="1" r:id="rId1"/>
@@ -253,10 +253,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2面牆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">全內周 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -362,6 +358,10 @@
   </si>
   <si>
     <t>男廁,女廁,殘障廁所,無障礙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1面牆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1042,16 +1042,16 @@
         <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>45</v>
@@ -1063,16 +1063,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="5">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="C2" s="6">
         <v>-0.1</v>
       </c>
       <c r="D2" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" s="6">
         <v>0.06</v>
@@ -1087,16 +1087,16 @@
     </row>
     <row r="3" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C3" s="6">
         <v>-0.1</v>
       </c>
       <c r="D3" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" s="6">
         <v>0.06</v>
@@ -1120,7 +1120,7 @@
         <v>-0.1</v>
       </c>
       <c r="D4" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" s="6">
         <v>0.06</v>
@@ -1138,13 +1138,13 @@
         <v>39</v>
       </c>
       <c r="B5" s="5">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="C5" s="6">
         <v>-0.1</v>
       </c>
       <c r="D5" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" s="6">
         <v>0.06</v>
@@ -1162,13 +1162,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="5">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="C6" s="6">
         <v>-0.1</v>
       </c>
       <c r="D6" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" s="6">
         <v>0.06</v>
@@ -1192,7 +1192,7 @@
         <v>-0.1</v>
       </c>
       <c r="D7" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" s="6">
         <v>0.06</v>
@@ -1210,13 +1210,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="5">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C8" s="6">
         <v>-0.1</v>
       </c>
       <c r="D8" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" s="6">
         <v>0.06</v>
@@ -1234,13 +1234,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="5">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C9" s="6">
         <v>-0.1</v>
       </c>
       <c r="D9" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" s="6">
         <v>0.06</v>
@@ -1264,7 +1264,7 @@
         <v>-0.1</v>
       </c>
       <c r="D10" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" s="6">
         <v>0.06</v>
@@ -1307,16 +1307,16 @@
         <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>45</v>
@@ -1328,16 +1328,16 @@
     </row>
     <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="5">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="C2" s="6">
         <v>-0.1</v>
       </c>
       <c r="D2" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" s="6">
         <v>0.06</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="5">
         <v>650</v>
@@ -1361,7 +1361,7 @@
         <v>-0.1</v>
       </c>
       <c r="D3" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" s="6">
         <v>0.06</v>
@@ -1376,7 +1376,7 @@
     </row>
     <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5">
         <v>650</v>
@@ -1385,7 +1385,7 @@
         <v>-0.1</v>
       </c>
       <c r="D4" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" s="6">
         <v>0.06</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5">
         <v>500</v>
@@ -1409,7 +1409,7 @@
         <v>-0.1</v>
       </c>
       <c r="D5" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" s="6">
         <v>0.06</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="5">
         <v>600</v>
@@ -1433,7 +1433,7 @@
         <v>-0.1</v>
       </c>
       <c r="D6" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" s="6">
         <v>0.06</v>
@@ -1448,7 +1448,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="5">
         <v>700</v>
@@ -1457,7 +1457,7 @@
         <v>-0.1</v>
       </c>
       <c r="D7" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" s="6">
         <v>0.06</v>
@@ -1472,7 +1472,7 @@
     </row>
     <row r="8" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="5">
         <v>660</v>
@@ -1481,7 +1481,7 @@
         <v>-0.1</v>
       </c>
       <c r="D8" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" s="6">
         <v>0.06</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="5">
         <v>450</v>
@@ -1505,7 +1505,7 @@
         <v>-0.1</v>
       </c>
       <c r="D9" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" s="6">
         <v>0.06</v>
@@ -1529,7 +1529,7 @@
         <v>-0.1</v>
       </c>
       <c r="D10" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" s="6">
         <v>0.06</v>
@@ -1563,16 +1563,16 @@
         <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>45</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="2" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="5">
         <v>630</v>
@@ -1593,7 +1593,7 @@
         <v>-0.1</v>
       </c>
       <c r="D2" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" s="6">
         <v>0.06</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="5">
         <v>650</v>
@@ -1617,7 +1617,7 @@
         <v>-0.1</v>
       </c>
       <c r="D3" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" s="6">
         <v>0.06</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5">
         <v>550</v>
@@ -1641,7 +1641,7 @@
         <v>-0.1</v>
       </c>
       <c r="D4" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" s="6">
         <v>0.06</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5">
         <v>450</v>
@@ -1665,7 +1665,7 @@
         <v>-0.1</v>
       </c>
       <c r="D5" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" s="6">
         <v>0.06</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="5">
         <v>400</v>
@@ -1689,7 +1689,7 @@
         <v>-0.1</v>
       </c>
       <c r="D6" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" s="6">
         <v>0.06</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="5">
         <v>700</v>
@@ -1713,7 +1713,7 @@
         <v>-0.1</v>
       </c>
       <c r="D7" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" s="6">
         <v>0.06</v>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="5">
         <v>660</v>
@@ -1737,7 +1737,7 @@
         <v>-0.1</v>
       </c>
       <c r="D8" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" s="6">
         <v>0.06</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" s="5">
         <v>450</v>
@@ -1761,7 +1761,7 @@
         <v>-0.1</v>
       </c>
       <c r="D9" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" s="6">
         <v>0.06</v>
@@ -1785,7 +1785,7 @@
         <v>-0.1</v>
       </c>
       <c r="D10" s="6">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" s="6">
         <v>0.06</v>
